--- a/IKEA_Workspace_Planner_REF/Data/Input.xlsx
+++ b/IKEA_Workspace_Planner_REF/Data/Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasem\OneDrive\Desktop\IkeaProject\IKEA_Workspace_Planner_REF\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7FA58C-9467-4FBF-9E03-D2BA13C02E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949993B1-1B74-4D2C-B8F7-3790C23A85C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{AC91FF8C-B103-4544-86DD-45EF6E7548E4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AC91FF8C-B103-4544-86DD-45EF6E7548E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Requests" sheetId="1" r:id="rId1"/>
@@ -36,20 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Category</t>
   </si>
   <si>
-    <t xml:space="preserve">SearchKeyword </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxPriceRON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PreferredKeyword </t>
-  </si>
-  <si>
     <t>TopN</t>
   </si>
   <si>
@@ -71,7 +62,10 @@
     <t>Lamp</t>
   </si>
   <si>
-    <t xml:space="preserve">xyzxyz </t>
+    <t>MaxPriceRON</t>
+  </si>
+  <si>
+    <t>SearchKeyword</t>
   </si>
 </sst>
 </file>
@@ -443,74 +437,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B96AB3-FAFD-440D-9DF9-BC4052064850}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.73046875" customWidth="1"/>
     <col min="3" max="3" width="13.19921875" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
       </c>
       <c r="C2">
         <v>500</v>
       </c>
-      <c r="E2">
+      <c r="D2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="D3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>200</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
         <v>5</v>
       </c>
     </row>

--- a/IKEA_Workspace_Planner_REF/Data/Input.xlsx
+++ b/IKEA_Workspace_Planner_REF/Data/Input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasem\OneDrive\Desktop\IkeaProject\IKEA_Workspace_Planner_REF\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949993B1-1B74-4D2C-B8F7-3790C23A85C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49755F3-A8AB-479F-90EA-EAD9860C5335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AC91FF8C-B103-4544-86DD-45EF6E7548E4}"/>
   </bookViews>
@@ -482,7 +482,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="D3">
         <v>5</v>
